--- a/Convert_from_xlsx_to_Json/table_normalization/economy-table33.xlsx
+++ b/Convert_from_xlsx_to_Json/table_normalization/economy-table33.xlsx
@@ -250,11 +250,11 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="5">
-    <numFmt numFmtId="167" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="168" formatCode="&quot;$&quot;#,##0.00"/>
-    <numFmt numFmtId="169" formatCode="0.0"/>
-    <numFmt numFmtId="170" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
-    <numFmt numFmtId="171" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.00"/>
+    <numFmt numFmtId="166" formatCode="0.0"/>
+    <numFmt numFmtId="167" formatCode="&quot;$&quot;#,##0.00_);[Red]\(&quot;$&quot;#,##0.00\)"/>
+    <numFmt numFmtId="168" formatCode="_-&quot;$&quot;* #,##0.00_-;\-&quot;$&quot;* #,##0.00_-;_-&quot;$&quot;* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="5">
     <font>
@@ -360,7 +360,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -378,7 +378,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -387,26 +387,26 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="169" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="170" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="167" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
@@ -417,7 +417,7 @@
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -438,7 +438,7 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="1" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -453,15 +453,15 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="168" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="165" fontId="3" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="169" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="2" xfId="2" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -478,18 +478,18 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="170" fontId="2" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="167" fontId="2" fillId="3" borderId="2" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="2" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="3" borderId="0" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="9" fontId="2" fillId="3" borderId="2" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -498,20 +498,20 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="168" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="171" fontId="2" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="171" fontId="2" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="2" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="168" fontId="2" fillId="4" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="171" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="168" fontId="2" fillId="3" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
